--- a/artfynd/A 58070-2022 artfynd.xlsx
+++ b/artfynd/A 58070-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 58070-2022 artfynd.xlsx
+++ b/artfynd/A 58070-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -877,6 +877,131 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>121650564</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57689</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103008</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Ärtsångare</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Curruca curruca</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Gottne, Ång</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>669456</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7038923</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Mo</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-05-15</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>05:37</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-05-15</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>05:37</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Sanna Pousar</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>SPR0002 Artinventering Gottne</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 58070-2022 artfynd.xlsx
+++ b/artfynd/A 58070-2022 artfynd.xlsx
@@ -882,7 +882,7 @@
         <v>121650564</v>
       </c>
       <c r="B4" t="n">
-        <v>57690</v>
+        <v>57698</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 58070-2022 artfynd.xlsx
+++ b/artfynd/A 58070-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610741</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610742</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -986,6 +1001,11 @@
           <t>SPR0002 Artinventering Gottne</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121650559</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1106,8 +1126,19 @@
           <t>SPR0002 Artinventering Gottne</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121650564</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>